--- a/EXCEL/Exercise Files/Chapter04/04_04_Poisson.xlsx
+++ b/EXCEL/Exercise Files/Chapter04/04_04_Poisson.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0694DC43-4D07-41D7-A71E-DDD29B0B73BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3521D67-5BB1-430F-8CE9-0B1A81D6BCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="288" yWindow="324" windowWidth="22752" windowHeight="11916" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -266,61 +265,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>9.1188196555451624E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>6.3831737588816127E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>2.2341108156085653E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>5.2129252364199866E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>9.1226191637349782E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.12771666829228964</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.14900277967433789</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.14900277967433789</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.13037743221504566</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>0.10140466950059109</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>7.0983268650413753E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>4.5171170959354211E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>2.6349849726289985E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>1.4188380621848417E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>7.0941903109242224E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>3.3106221450979714E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>1.4483971884803614E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>5.9639884231544313E-4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>2.3193288312267158E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -477,6 +476,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -484,7 +484,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1380,12 +1379,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -1399,162 +1398,181 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f>_xlfn.POISSON.DIST(A2,$E$1,FALSE)</f>
+        <v>9.1188196555451624E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" ref="B3:B20" si="0">_xlfn.POISSON.DIST(A3,$E$1,FALSE)</f>
+        <v>6.3831737588816127E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>2.2341108156085653E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>5.2129252364199866E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>9.1226191637349782E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>0.12771666829228964</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>0.14900277967433789</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>0.14900277967433789</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>0.13037743221504566</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>0.10140466950059109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>7.0983268650413753E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>4.5171170959354211E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>2.6349849726289985E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>1.4188380621848417E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>7.0941903109242224E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>3.3106221450979714E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>1.4483971884803614E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>5.9639884231544313E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>2.3193288312267158E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B21" s="2"/>
     </row>
-    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B22" s="2"/>
     </row>
   </sheetData>
